--- a/actividades.xlsx
+++ b/actividades.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -545,6 +545,66 @@
         </is>
       </c>
       <c r="L2" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Realizar seguimiento a solicitudes y requerimientos tecnológicos de los usuarios, documentando novedades, avances y necesidades adicionales, y comunicándolas oportunamente a los responsables correspondientes.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-02-13 12:00:22</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>COMUNICACIONES</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Valentina</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>APOYO TECNOLÓGICO</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>LLAMADA TELEFONICA</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Se solicita la revisión de un problema con la aplicación de lectura de los archivos, se hace la revisión correspondiente y se instala una aplicación de lectura de archivos diferente al solicitante, se le informa al solicitante sobre esto</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Se solicita la revisión de un problema con la aplicación de lectura de los archivos, se hace la revisión correspondiente y se instala una aplicación de lectura de archivos diferente al solicitante, se le informa al solicitante sobre esto</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>admin</t>
         </is>

--- a/actividades.xlsx
+++ b/actividades.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -607,6 +607,66 @@
       <c r="L3" t="inlineStr">
         <is>
           <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Apoyar en el mantenimiento preventivo básico de equipos tecnológicos, realizando tareas como limpieza, revisión de cables, conectores y periféricos, con el objetivo de mantener en condiciones óptimas los recursos informáticos de la entidad.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-02-16 11:32:34</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ALCALDÍA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Prueba</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO PREVENTIVO</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>LLAMADA TELEFONICA</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Prueba</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Prueba</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
         </is>
       </c>
     </row>

--- a/actividades.xlsx
+++ b/actividades.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,186 +487,6 @@
       <c r="L1" s="1" t="inlineStr">
         <is>
           <t>USUARIO</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Colaborar en la implementación y seguimiento de medidas básicas de seguridad informática, tales como el monitoreo de alertas básicas, cierre adecuado de sesiones y cumplimiento de rutinas establecidas para el uso seguro de los recursos tecnológicos.</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-02-09 09:00:06</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ALCALDÍA</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Prueba</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO CORRECTIVO</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>INTRANET</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Prueba</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Prueba</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Realizar seguimiento a solicitudes y requerimientos tecnológicos de los usuarios, documentando novedades, avances y necesidades adicionales, y comunicándolas oportunamente a los responsables correspondientes.</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-02-13 12:00:22</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>COMUNICACIONES</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Valentina</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>APOYO TECNOLÓGICO</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>LLAMADA TELEFONICA</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Se solicita la revisión de un problema con la aplicación de lectura de los archivos, se hace la revisión correspondiente y se instala una aplicación de lectura de archivos diferente al solicitante, se le informa al solicitante sobre esto</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Se solicita la revisión de un problema con la aplicación de lectura de los archivos, se hace la revisión correspondiente y se instala una aplicación de lectura de archivos diferente al solicitante, se le informa al solicitante sobre esto</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Apoyar en el mantenimiento preventivo básico de equipos tecnológicos, realizando tareas como limpieza, revisión de cables, conectores y periféricos, con el objetivo de mantener en condiciones óptimas los recursos informáticos de la entidad.</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-02-16 11:32:34</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ALCALDÍA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Prueba</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>MANTENIMIENTO PREVENTIVO</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>LLAMADA TELEFONICA</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Prueba</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2026-02-16</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Prueba</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Alejandro</t>
         </is>
       </c>
     </row>

--- a/actividades.xlsx
+++ b/actividades.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,68 +413,1488 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>USUARIO</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
         <is>
           <t>TIPO DE ACTIVIDAD</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>FECHA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DEPENDENCIA</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>SOLICITANTE</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>TIPO DE SOLICITUD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>MEDIO DE SOLICITUD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>DESCRIPCIÓN</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>CUMPLIDO</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>FECHA ATENCIÓN</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>OBSERVACIONES</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>USUARIO</t>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1.	Brindar apoyo en la atención de requerimientos técnicos de primer nivel a los usuarios de la Administración Municipal, atendiendo incidentes relacionados con el funcionamiento de equipos de cómputo, impresoras, configuración de software y otros periféricos.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-03-09 10:40:34</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>BIBLIOTECAS</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Saudith</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>APOYO TECNOLÓGICO</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>LLAMADA TELEFONICA</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Se solicita la visita y solicitud a la biblioteca para la revision de la intermitencia del internet, se radica la solicitud a tigo une</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Se solicita la visita y solicitud a la biblioteca para la revision de la intermitencia del internet, se radica la solicitud a tigo une</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1.	Brindar apoyo en la atención de requerimientos técnicos de primer nivel a los usuarios de la Administración Municipal, atendiendo incidentes relacionados con el funcionamiento de equipos de cómputo, impresoras, configuración de software y otros periféricos.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-03-09 10:49:07</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>IMPUESTOS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Elizabeth</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>APOYO TECNOLÓGICO</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Se solicita la asignación de permisos a un funcionario nuevo, se hace la asignación de permisos pertinente, se le informa a la solicitante la asignación de estos permisos </t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Se solicita la asignación de permisos a un funcionario nuevo, se hace la asignación de permisos pertinente, se le informa a la solicitante la asignación de estos permisos </t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>6.	Apoyar en la documentación técnica del área, incluyendo la organización y archivo de documentos, informes de soporte y demás registros, de acuerdo con las directrices internas y del Sistema de Gestión de Calidad.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-03-09 10:52:03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ARCHIVO GENERAL</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Edwin</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>APOYO TECNOLÓGICO</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Se solicita la asignación de permisos necesarios para continuar con la función y son necesario para el solicitante, se asignan los permisos solicitados y se le informa al solicitante</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Se solicita la asignación de permisos necesarios para continuar con la función y son necesario para el solicitante, se asignan los permisos solicitados y se le informa al solicitante</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>6.	Apoyar en la documentación técnica del área, incluyendo la organización y archivo de documentos, informes de soporte y demás registros, de acuerdo con las directrices internas y del Sistema de Gestión de Calidad.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-03-09 11:24:20</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CATASTRO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Yolanda</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>APOYO TECNOLÓGICO</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Se solicita la creación y asignación de permisos a un nuevo funcionario, se hace los requerimientos solicitados y se le informan a la solicitante </t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Se solicita la creación y asignación de permisos a un nuevo funcionario, se hace los requerimientos solicitados y se le informan a la solicitante </t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>6.	Apoyar en la documentación técnica del área, incluyendo la organización y archivo de documentos, informes de soporte y demás registros, de acuerdo con las directrices internas y del Sistema de Gestión de Calidad.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-03-10 15:11:18</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>IMPUESTOS</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Elizabeth</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>APOYO TECNOLÓGICO</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Se solicita la asignación de permisos a un funcionario, se asignan los permisos solicitados y se le informa a la solicitante</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Se solicita la asignación de permisos a un funcionario, se asignan los permisos solicitados y se le informa a la solicitante</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>4.	Apoyar en tareas logísticas relacionadas con la infraestructura tecnológica, tales como instalación, traslado o reubicación de equipos de cómputo, dispositivos de red y demás componentes tecnológicos, bajo supervisión del personal del área.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-03-11 15:12:49</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>INFRAESTRUCTURA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>APOYO TECNOLÓGICO</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Se solicita la instalación de nueva impresora en la oficina de Familia, se hace la instalación respectiva y se evidencia el funcionamiento de la impresora</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Se solicita la instalación de nueva impresora en la oficina de Familia, se hace la instalación respectiva y se evidencia el funcionamiento de la impresora</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1.	Brindar apoyo en la atención de requerimientos técnicos de primer nivel a los usuarios de la Administración Municipal, atendiendo incidentes relacionados con el funcionamiento de equipos de cómputo, impresoras, configuración de software y otros periféricos.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-03-10 15:20:23</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>FAMILIA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Alejandra</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>APOYO TECNOLÓGICO</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>VERBAL</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Se solicita la instalación de la impresora en el equipo, se hace la instalación respectiva y se le evidencia a la solicitante</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Se solicita la instalación de la impresora en el equipo, se hace la instalación respectiva y se le evidencia a la solicitante</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1.	Brindar apoyo en la atención de requerimientos técnicos de primer nivel a los usuarios de la Administración Municipal, atendiendo incidentes relacionados con el funcionamiento de equipos de cómputo, impresoras, configuración de software y otros periféricos.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-03-10 15:22:53</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>FAMILIA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Alejandra</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>APOYO TECNOLÓGICO</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>VERBAL</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Se solicita la instalación del escáner en el equipo, se hace la instalación con permiso del jefe inmediado de la solicitante y se evidencia la solicitante</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Se solicita la instalación del escáner en el equipo, se hace la instalación con permiso del jefe inmediado de la solicitante y se evidencia la solicitante</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1.	Brindar apoyo en la atención de requerimientos técnicos de primer nivel a los usuarios de la Administración Municipal, atendiendo incidentes relacionados con el funcionamiento de equipos de cómputo, impresoras, configuración de software y otros periféricos.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-03-10 15:24:18</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>FAMILIA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Patricia</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>APOYO TECNOLÓGICO</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>VERBAL</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Se solicita la instalación del escáner con permiso del jefe inmediato de la solicitante, se hace la instalación respectiva y se le evidencia el funcionamiento </t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Se solicita la instalación del escáner con permiso del jefe inmediato de la solicitante, se hace la instalación respectiva y se le evidencia el funcionamiento </t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>4.	Apoyar en tareas logísticas relacionadas con la infraestructura tecnológica, tales como instalación, traslado o reubicación de equipos de cómputo, dispositivos de red y demás componentes tecnológicos, bajo supervisión del personal del área.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-03-10 08:12:39</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>FAMILIA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>APOYO TECNOLÓGICO</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>VERBAL</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Se solicita la instalación de una nueva impresora en el puesto del solicitante, se hace la instalación respectiva y e l evidencia al solicitante el funcionamiento correcto de la impresora</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Se solicita la instalación de una nueva impresora en el puesto del solicitante, se hace la instalación respectiva y e l evidencia al solicitante el funcionamiento correcto de la impresora</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>6.	Apoyar en la documentación técnica del área, incluyendo la organización y archivo de documentos, informes de soporte y demás registros, de acuerdo con las directrices internas y del Sistema de Gestión de Calidad.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-03-11 08:16:56</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>OFICINA DE SISTEMAS</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Felipe</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ASESORIA Y ASISTENCIA</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Se solicita el acompañamiento de la capacitación del personal de Saimyr, se hace el acompañamiento respectivo y recolección de firmas necesario</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Se solicita el acompañamiento de la capacitación del personal de Saimyr, se hace el acompañamiento respectivo y recolección de firmas necesario</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1.	Brindar apoyo en la atención de requerimientos técnicos de primer nivel a los usuarios de la Administración Municipal, atendiendo incidentes relacionados con el funcionamiento de equipos de cómputo, impresoras, configuración de software y otros periféricos.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-03-11 08:20:20</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ALMACEN MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Marcela</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>APOYO TECNOLÓGICO</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>VERBAL</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Se solicita la instalación del escáner al equipo de la solicitante, se hace la instalación respectiva y se le evidencia a la solicitante el funcionamiento normal del escáner</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Se solicita la instalación del escáner al equipo de la solicitante, se hace la instalación respectiva y se le evidencia a la solicitante el funcionamiento normal del escáner</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2.	Apoyar en el mantenimiento preventivo básico de equipos tecnológicos, realizando tareas como limpieza, revisión de cables, conectores y periféricos, con el objetivo de mantener en condiciones óptimas los recursos informáticos de la entidad.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-03-11 08:22:25</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ALMACEN MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Felipe</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO PREVENTIVO</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>VERBAL</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Se solicita la eliminación de las impresoras que están instaladas en el equipo pero ya no se encuentran, se hace la eliminación respectiva y se le evidencia al funcionario</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Se solicita la eliminación de las impresoras que están instaladas en el equipo pero ya no se encuentran, se hace la eliminación respectiva y se le evidencia al funcionario</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>4.	Apoyar en tareas logísticas relacionadas con la infraestructura tecnológica, tales como instalación, traslado o reubicación de equipos de cómputo, dispositivos de red y demás componentes tecnológicos, bajo supervisión del personal del área.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:33:18</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>OFICINA DE SISTEMAS</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Mario Henao</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>APOYO TECNOLÓGICO</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>VERBAL</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Se solicita el traslado de equipos dados de baja a los inservibles, se hace el traslado respectivo de estos equipos</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Se solicita el traslado de equipos dados de baja a los inservibles, se hace el traslado respectivo de estos equipos</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>5.	Realizar seguimiento a solicitudes y requerimientos tecnológicos de los usuarios, documentando novedades, avances y necesidades adicionales, y comunicándolas oportunamente a los responsables correspondientes.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-03-12 08:39:22</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>IMPUESTOS</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Elizabeth</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ASESORIA Y ASISTENCIA</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Se solicita la asignación de permisos de fiscales a los funcionarios, se hace la solicitud de permisos al encargado del modulo de ejecuciones fiscales se asignan los permisos solicitados</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Se solicita la asignación de permisos de fiscales a los funcionarios, se hace la solicitud de permisos al encargado del modulo de ejecuciones fiscales se asignan los permisos solicitados</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1.	Brindar apoyo en la atención de requerimientos técnicos de primer nivel a los usuarios de la Administración Municipal, atendiendo incidentes relacionados con el funcionamiento de equipos de cómputo, impresoras, configuración de software y otros periféricos.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-03-13 08:52:39</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>BIBLIOTECAS</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Saudith</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ASESORIA Y ASISTENCIA</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Se solicita la revisión y acompañamiento el personal de Tigo, se acompaña y se revisa y se plantea un cambio de equipo desde el técnico de Tigo</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Se solicita la revisión y acompañamiento el personal de Tigo, se acompaña y se revisa y se plantea un cambio de equipo desde el técnico de Tigo</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5.	Realizar seguimiento a solicitudes y requerimientos tecnológicos de los usuarios, documentando novedades, avances y necesidades adicionales, y comunicándolas oportunamente a los responsables correspondientes.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-03-13 08:57:31</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>EJECUCIONES FISCALES</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>APOYO TECNOLÓGICO</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Se solicita la creación de un nuevo usuario para un nuevo funcionario en la dependencia, se hace la solicitud respectiva a los encargados de la plataforma Saimyr, se informa del nuevo usuario al solicitante</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Se solicita la creación de un nuevo usuario para un nuevo funcionario en la dependencia, se hace la solicitud respectiva a los encargados de la plataforma Saimyr, se informa del nuevo usuario al solicitante</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1.	Brindar apoyo en la atención de requerimientos técnicos de primer nivel a los usuarios de la Administración Municipal, atendiendo incidentes relacionados con el funcionamiento de equipos de cómputo, impresoras, configuración de software y otros periféricos.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-03-16 11:11:55</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>BIBLIOTECAS</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Saudith</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ASESORIA Y ASISTENCIA</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Se solicita el acompañamiento en el cambio de equipo que estaba presentando el problema de interrupciones en el servicio de internet, se revisa que los servicios sigan funcionando</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Se solicita el acompañamiento en el cambio de equipo que estaba presentando el problema de interrupciones en el servicio de internet, se revisa que los servicios sigan funcionando</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>7.	Colaborar en la implementación y seguimiento de medidas básicas de seguridad informática, tales como el monitoreo de alertas básicas, cierre adecuado de sesiones, y cumplimiento de rutinas establecidas para el uso seguro de los recursos tecnológicos.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-03-16 11:25:03</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>EJECUCIONES FISCALES</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Jarol</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>APOYO TECNOLÓGICO</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>VERBAL</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Se solicita cambio de contraseña de acceso al modulo del solicitante, se hace el cambio solicitado y se le informa al solicitante</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Se solicita cambio de contraseña de acceso al modulo del solicitante, se hace el cambio solicitado y se le informa al solicitante</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>5.	Realizar seguimiento a solicitudes y requerimientos tecnológicos de los usuarios, documentando novedades, avances y necesidades adicionales, y comunicándolas oportunamente a los responsables correspondientes.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-03-16 11:36:51</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>EJECUCIONES FISCALES</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>APOYO TECNOLÓGICO</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Se solicita la asignación de permisos al usuario solicitado, se asignan los permisos solicitados y se le informa al solicitante</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Se solicita la asignación de permisos al usuario solicitado, se asignan los permisos solicitados y se le informa al solicitante</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>5.	Realizar seguimiento a solicitudes y requerimientos tecnológicos de los usuarios, documentando novedades, avances y necesidades adicionales, y comunicándolas oportunamente a los responsables correspondientes.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-03-23 11:56:35</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>IMPUESTOS</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Elizabeth</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>APOYO TECNOLÓGICO</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Se solicita la inhabilitación de módulos y eliminación de usuario para un funcionario que ya no se encuentra en la dependencia</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Se solicita la inhabilitación de módulos y eliminación de usuario para un funcionario que ya no se encuentra en la dependencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1.	Brindar apoyo en la atención de requerimientos técnicos de primer nivel a los usuarios de la Administración Municipal, atendiendo incidentes relacionados con el funcionamiento de equipos de cómputo, impresoras, configuración de software y otros periféricos.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-03-17 17:18:30</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>PLANEACIÓN</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Maribel</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO CORRECTIVE</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>LLAMADA TELEFONICA</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Se solicita la revisión de la impresora ya que esta salía una linea en el medio, se hace la revisión y limpieza respectiva y se le evidencia a la solicitante el funcionamiento normal de la impresora</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Se solicita la revisión de la impresora ya que esta salía una linea en el medio, se hace la revisión y limpieza respectiva y se le evidencia a la solicitante el funcionamiento normal de la impresora</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1.	Brindar apoyo en la atención de requerimientos técnicos de primer nivel a los usuarios de la Administración Municipal, atendiendo incidentes relacionados con el funcionamiento de equipos de cómputo, impresoras, configuración de software y otros periféricos.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-03-17 17:21:20</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PLANEACIÓN</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>MANTENIMIENTO CORRECTIVE</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>VERBAL</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Se solicita la revisión de la impresora pues salía un fallo al imprimir, se instala el driver correspondiente de la impresora y se evidencia el correcto funcionamiento de la impresora</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Se solicita la revisión de la impresora pues salía un fallo al imprimir, se instala el driver correspondiente de la impresora y se evidencia el correcto funcionamiento de la impresora</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>5.	Realizar seguimiento a solicitudes y requerimientos tecnológicos de los usuarios, documentando novedades, avances y necesidades adicionales, y comunicándolas oportunamente a los responsables correspondientes.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-03-18 13:54:04</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>IMPUESTOS</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Elizabeth</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>APOYO TECNOLÓGICO</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Se solicita retirar los permisos en los módulos a funcionarios que ya no están en la administración o en la oficina de impuestos</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Se solicita retirar los permisos en los módulos a funcionarios que ya no están en la administración o en la oficina de impuestos</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>6.	Apoyar en la documentación técnica del área, incluyendo la organización y archivo de documentos, informes de soporte y demás registros, de acuerdo con las directrices internas y del Sistema de Gestión de Calidad.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-03-18 13:57:12</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>FAMILIA</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Luis Alejandro</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>APOYO TECNOLÓGICO</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Se solicita la creación de un nuevo correo para el apoyo de la nueva psicóloga, se hace la creación del nuevo correo y se le informa al solicitante</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Se solicita la creación de un nuevo correo para el apoyo de la nueva psicóloga, se hace la creación del nuevo correo y se le informa al solicitante</t>
         </is>
       </c>
     </row>

--- a/actividades.xlsx
+++ b/actividades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1898,6 +1898,1032 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>8.	Apoyar en otras actividades de carácter técnico-operativo o administrativo relacionadas con la gestión de tecnologías de la información, que le sean asignadas por el supervisor del contrato o el Ordenador del Gasto, en concordancia con el objeto contractual.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-03-19 09:03:51</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>OFICINA DE SISTEMAS</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Mario Henao</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>VERBAL</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Se solicita la creación de un software para gestionar las actividades, se realiza la creación del software, se realiza la impletación y se le evidencia al funcionario el funcionamiento del software</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Se solicita la creación de un software para gestionar las actividades, se realiza la creación del software, se realiza la impletación y se le evidencia al funcionario el funcionamiento del software</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>5.	Realizar seguimiento a solicitudes y requerimientos tecnológicos de los usuarios, documentando novedades, avances y necesidades adicionales, y comunicándolas oportunamente a los responsables correspondientes.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-03-19 09:25:43</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CONTROL INTERNO</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Leopoldo</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>VERBAL</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Se solicita la revisión de una tablet, se hace la revision correspondiente y se le envia el diagnostico a la persona encargada </t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Se solicita la revisión de una tablet, se hace la revision correspondiente y se le envia el diagnostico a la persona encargada </t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>6.	Apoyar en la documentación técnica del área, incluyendo la organización y archivo de documentos, informes de soporte y demás registros, de acuerdo con las directrices internas y del Sistema de Gestión de Calidad.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-03-20 09:33:01</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>MOVILIDAD</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Leonardo</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Se solicita el cambio de contraseña del acceso a la intranet, se hace el cambio respectivo y se le informa al solicitante</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Se solicita el cambio de contraseña del acceso a la intranet, se hace el cambio respectivo y se le informa al solicitante</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1.	Brindar apoyo en la atención de requerimientos técnicos de primer nivel a los usuarios de la Administración Municipal, atendiendo incidentes relacionados con el funcionamiento de equipos de cómputo, impresoras, configuración de software y otros periféricos.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-03-23 10:15:57</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>INFRAESTRUCTURA</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Sebastian</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Impresoras</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>VERBAL</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Se solicita la recarga de tinta de la impresora, se hace la recarga respectiva y se le evidencia al funcionario</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Se solicita la recarga de tinta de la impresora, se hace la recarga respectiva y se le evidencia al funcionario</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1.	Brindar apoyo en la atención de requerimientos técnicos de primer nivel a los usuarios de la Administración Municipal, atendiendo incidentes relacionados con el funcionamiento de equipos de cómputo, impresoras, configuración de software y otros periféricos.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-03-23 08:05:28</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>INFRAESTRUCTURA</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Diana</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Impresoras</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>VERBAL</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Se solicita la revisión de la conexion con la impresora y el por que solicita revision de papel a la hora de imprimir, se hace la revisión respectiva y se hace el cambio de configuracion, se evidencaia al soliciante el funcionamiento</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Se solicita la revisión de la conexion con la impresora y el por que solicita revision de papel a la hora de imprimir, se hace la revisión respectiva y se hace el cambio de configuracion, se evidencaia al soliciante el funcionamiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1.	Brindar apoyo en la atención de requerimientos técnicos de primer nivel a los usuarios de la Administración Municipal, atendiendo incidentes relacionados con el funcionamiento de equipos de cómputo, impresoras, configuración de software y otros periféricos.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-03-23 08:05:48</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>INFRAESTRUCTURA</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Impresoras</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>VERBAL</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Se solicita la revisión de la conexion con la impresora y el por que solicita revision de papel a la hora de imprimir, se hace la revisión respectiva y se hace el cambio de configuracion, se evidencaia al soliciante el funcionamiento</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Se solicita la revisión de la conexion con la impresora y el por que solicita revision de papel a la hora de imprimir, se hace la revisión respectiva y se hace el cambio de configuracion, se evidencaia al soliciante el funcionamiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1.	Brindar apoyo en la atención de requerimientos técnicos de primer nivel a los usuarios de la Administración Municipal, atendiendo incidentes relacionados con el funcionamiento de equipos de cómputo, impresoras, configuración de software y otros periféricos.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-03-23 08:06:09</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>INFRAESTRUCTURA</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Nelly</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Impresoras</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>VERBAL</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Se solicita la revisión de la conexion con la impresora y el por que solicita revision de papel a la hora de imprimir, se hace la revisión respectiva y se hace el cambio de configuracion, se evidencaia al soliciante el funcionamiento</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Se solicita la revisión de la conexion con la impresora y el por que solicita revision de papel a la hora de imprimir, se hace la revisión respectiva y se hace el cambio de configuracion, se evidencaia al soliciante el funcionamiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1.	Brindar apoyo en la atención de requerimientos técnicos de primer nivel a los usuarios de la Administración Municipal, atendiendo incidentes relacionados con el funcionamiento de equipos de cómputo, impresoras, configuración de software y otros periféricos.</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-03-23 08:08:32</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>PLANEACIÓN</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Sebastian</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Impresoras</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>VERBAL</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Se solicita la recarga de tinta en la impresora, se hace la recarga respectiva y se le informa al solicitante</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Se solicita la recarga de tinta en la impresora, se hace la recarga respectiva y se le informa al solicitante</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2.	Apoyar en el mantenimiento preventivo básico de equipos tecnológicos, realizando tareas como limpieza, revisión de cables, conectores y periféricos, con el objetivo de mantener en condiciones óptimas los recursos informáticos de la entidad.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-03-23 08:10:21</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ARCHIVO GENERAL</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Edwin</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Impresoras</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>VERBAL</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Se solicita la revision de la impresora ya que al imprimir las ojas salian con imperfectos que reducian la legibilidad, se hace la limpieza al rodillo del toner y a la impresora y se le evidencia al funcionario el normal funcionamiento </t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Se solicita la revision de la impresora ya que al imprimir las ojas salian con imperfectos que reducian la legibilidad, se hace la limpieza al rodillo del toner y a la impresora y se le evidencia al funcionario el normal funcionamiento </t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1.	Brindar apoyo en la atención de requerimientos técnicos de primer nivel a los usuarios de la Administración Municipal, atendiendo incidentes relacionados con el funcionamiento de equipos de cómputo, impresoras, configuración de software y otros periféricos.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-03-23 08:20:52</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CASA DE JUSTICIA</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Maria Isabel</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Impresoras</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>VERBAL</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Se solicita la recarga de tinta en la impresora y revisar la conexion con esta, se hace la revisión respeciva y se le deja evidenciado al solicitante el funcionamiento normal de esta</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Se solicita la recarga de tinta en la impresora y revisar la conexion con esta, se hace la revisión respeciva y se le deja evidenciado al solicitante el funcionamiento normal de esta</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>7.	Colaborar en la implementación y seguimiento de medidas básicas de seguridad informática, tales como el monitoreo de alertas básicas, cierre adecuado de sesiones, y cumplimiento de rutinas establecidas para el uso seguro de los recursos tecnológicos.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-03-24 15:48:39</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>CATASTRO</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Adrian</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>VERBAL</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Se solicita el cambio de contraseña de ingreso al moulo de la plataforma, se hace el cambio respectivo y se le informa al solicitante</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Se solicita el cambio de contraseña de ingreso al moulo de la plataforma, se hace el cambio respectivo y se le informa al solicitante</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>3.	Colaborar en el control y actualización del inventario de activos tecnológicos, incluyendo equipos de cómputo, dispositivos de red, periféricos y demás recursos asignados a las dependencias, según los procedimientos establecidos por la oficina de sistemas.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-03-25 15:51:53</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>OFICINA DE SISTEMAS</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Felipe</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Hardware</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>VERBAL</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Se solicita acompañaiento en la revision de impresoras y verificacion de estas en el inventario</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Se solicita acompañaiento en la revision de impresoras y verificacion de estas en el inventario</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>8.	Apoyar en otras actividades de carácter técnico-operativo o administrativo relacionadas con la gestión de tecnologías de la información, que le sean asignadas por el supervisor del contrato o el Ordenador del Gasto, en concordancia con el objeto contractual.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-03-26 16:37:37</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ALCALDÍA</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Mario Henao</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Red/Conectividad</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>VERBAL</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Se solicita informar a el personal de la administración sobre el cambio en la red, se realiza el correo y se hace un seguimiento de las solicitudes</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Se solicita informar a el personal de la administración sobre el cambio en la red, se realiza el correo y se hace un seguimiento de las solicitudes</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2.	Apoyar en el mantenimiento preventivo básico de equipos tecnológicos, realizando tareas como limpieza, revisión de cables, conectores y periféricos, con el objetivo de mantener en condiciones óptimas los recursos informáticos de la entidad.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-03-26 16:38:43</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>EDUCACIÓN</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Erika</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Red/Conectividad</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>LLAMADA TELEFONICA</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Se solicita revisar la conectividad de varios equipos, se deja conectado 2 equipos a la red y se le deja evidenciado a los funcionarios</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Se solicita revisar la conectividad de varios equipos, se deja conectado 2 equipos a la red y se le deja evidenciado a los funcionarios</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>6.	Apoyar en la documentación técnica del área, incluyendo la organización y archivo de documentos, informes de soporte y demás registros, de acuerdo con las directrices internas y del Sistema de Gestión de Calidad.</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-03-27 16:40:52</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>OFICINA DE SISTEMAS</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Felipe</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Revisión</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Se solicita la revisión y terminación de la tarea de los sistemas de información solicitados para la gestión de calidad</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Se solicita la revisión y terminación de la tarea de los sistemas de información solicitados para la gestión de calidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>6.	Apoyar en la documentación técnica del área, incluyendo la organización y archivo de documentos, informes de soporte y demás registros, de acuerdo con las directrices internas y del Sistema de Gestión de Calidad.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-04-06 16:42:12</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>OFICINA DE SISTEMAS</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Mario Henao</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Revisión</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>VERBAL</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Se solicita la digitalización de la información de las impresoras y escáneres de la administración municipal</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Se solicita la digitalización de la información de las impresoras y escáneres de la administración municipal</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>6.	Apoyar en la documentación técnica del área, incluyendo la organización y archivo de documentos, informes de soporte y demás registros, de acuerdo con las directrices internas y del Sistema de Gestión de Calidad.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-04-07 16:43:58</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>OFICINA DE SISTEMAS</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Mario Henao</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Revisión</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>VERBAL</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Se solicita la creación y revisión de los indicadores de tecnología de acuerdo a gobierno digital, se realiza dicho archivo y se evidencian los datos obtenidos</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Se solicita la creación y revisión de los indicadores de tecnología de acuerdo a gobierno digital, se realiza dicho archivo y se evidencian los datos obtenidos</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>7.	Colaborar en la implementación y seguimiento de medidas básicas de seguridad informática, tales como el monitoreo de alertas básicas, cierre adecuado de sesiones, y cumplimiento de rutinas establecidas para el uso seguro de los recursos tecnológicos.</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-04-07 16:48:13</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>PLANEACIÓN</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Maria Angélica Balbin Rodriguez</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Se solicita la revisión de un email sospechoso, se revisa correspondientemente los datos y los links de dicho Email y se concluye que es un correo malicioso se procede a bloquear dicho correo desde donde se envió y se le informa a la solicitante</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Se solicita la revisión de un email sospechoso, se revisa correspondientemente los datos y los links de dicho Email y se concluye que es un correo malicioso se procede a bloquear dicho correo desde donde se envió y se le informa a la solicitante</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/actividades.xlsx
+++ b/actividades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>APOYO TECNOLÓGICO</t>
+          <t>Configuración</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2921,6 +2921,1146 @@
       <c r="K44" t="inlineStr">
         <is>
           <t>Se solicita la revisión de un email sospechoso, se revisa correspondientemente los datos y los links de dicho Email y se concluye que es un correo malicioso se procede a bloquear dicho correo desde donde se envió y se le informa a la solicitante</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>5.	Realizar seguimiento a solicitudes y requerimientos tecnológicos de los usuarios, documentando novedades, avances y necesidades adicionales, y comunicándolas oportunamente a los responsables correspondientes.</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-04-08 11:09:27</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>CONTABILIDAD</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Erica Marin</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Se solicita la asignacion de permisos requeridos, se hace la asignacion de permisos requeridos y se le informa a la solicitante</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Se solicita la asignacion de permisos requeridos, se hace la asignacion de permisos requeridos y se le informa a la solicitante</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>5.	Realizar seguimiento a solicitudes y requerimientos tecnológicos de los usuarios, documentando novedades, avances y necesidades adicionales, y comunicándolas oportunamente a los responsables correspondientes.</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-04-08 11:11:31</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>HACIENDA</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Yuliana Ruiz Jaramillo</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Se solicita la creación de un nuevo usuario para un nuevo contratista, se hace la solicitud respectiva a la mesa de Saimyr y se le informa el usuario a la solicitante </t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Se solicita la creación de un nuevo usuario para un nuevo contratista, se hace la solicitud respectiva a la mesa de Saimyr y se le informa el usuario a la solicitante </t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>6.	Apoyar en la documentación técnica del área, incluyendo la organización y archivo de documentos, informes de soporte y demás registros, de acuerdo con las directrices internas y del Sistema de Gestión de Calidad.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-04-09 11:12:40</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>HACIENDA</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Yuliana Ruiz Jaramillo</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Se solicita la asignación de permisos a un usuario, se hace la asignación de permisos requerida y se le informa a la solicitante</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Se solicita la asignación de permisos a un usuario, se hace la asignación de permisos requerida y se le informa a la solicitante</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>5.	Realizar seguimiento a solicitudes y requerimientos tecnológicos de los usuarios, documentando novedades, avances y necesidades adicionales, y comunicándolas oportunamente a los responsables correspondientes.</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-04-09 11:14:33</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>TESORERIA</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Steven</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Se solicita la creación de un usuario y los permisos respectivos a este, se hace la solicitud y se asignan los permisos requerido, se le informa al solicitante la información respectiva</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Se solicita la creación de un usuario y los permisos respectivos a este, se hace la solicitud y se asignan los permisos requerido, se le informa al solicitante la información respectiva</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>5.	Realizar seguimiento a solicitudes y requerimientos tecnológicos de los usuarios, documentando novedades, avances y necesidades adicionales, y comunicándolas oportunamente a los responsables correspondientes.</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-04-10 11:20:03</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ALMACEN MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Claudia Marcela Álvarez Chica</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Se solicita cambio de contraseña para el acceso a los modulo, se hace el cambio respectivo y se le informa a la solicitante</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Se solicita cambio de contraseña para el acceso a los modulo, se hace el cambio respectivo y se le informa a la solicitante</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>5.	Realizar seguimiento a solicitudes y requerimientos tecnológicos de los usuarios, documentando novedades, avances y necesidades adicionales, y comunicándolas oportunamente a los responsables correspondientes.</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-04-10 11:32:20</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>HACIENDA</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Lina Maria Rios</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Se solicita el cambio de contraseña para el acceso del usuario a los módulos, se hace el cambio de contraseña respectivo y se le deja evidenciado a la solicitante el funcionamiento de este</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Se solicita el cambio de contraseña para el acceso del usuario a los módulos, se hace el cambio de contraseña respectivo y se le deja evidenciado a la solicitante el funcionamiento de este</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>7.	Colaborar en la implementación y seguimiento de medidas básicas de seguridad informática, tales como el monitoreo de alertas básicas, cierre adecuado de sesiones, y cumplimiento de rutinas establecidas para el uso seguro de los recursos tecnológicos.</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-04-10 11:46:11</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>FAMILIA</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Luis Alejandro</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Red/Conectividad</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>LLAMADA TELEFONICA</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Se solicita el cambio de contraseña de ingreso al equipo de computo, se hace el cambio respectivo de acuerdo a los solicitado por el funcionario y se le deja evidenciado el normal funcionamiento</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Se solicita el cambio de contraseña de ingreso al equipo de computo, se hace el cambio respectivo de acuerdo a los solicitado por el funcionario y se le deja evidenciado el normal funcionamiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2.	Apoyar en el mantenimiento preventivo básico de equipos tecnológicos, realizando tareas como limpieza, revisión de cables, conectores y periféricos, con el objetivo de mantener en condiciones óptimas los recursos informáticos de la entidad.</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-04-10 13:52:08</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>FAMILIA</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Cristina</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>VERBAL</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Se solicita la instalación de un medio que pueda hacer copias de seguridad tiendo copia de seguridad del equipo y evitando perdida de archivos</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Se solicita la instalación de un medio que pueda hacer copias de seguridad tiendo copia de seguridad del equipo y evitando perdida de archivos</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>5.	Realizar seguimiento a solicitudes y requerimientos tecnológicos de los usuarios, documentando novedades, avances y necesidades adicionales, y comunicándolas oportunamente a los responsables correspondientes.</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-04-13 13:58:24</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>PLANEACIÓN</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Manuela Garcia Arroyave</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Se solicita la asignación de permisos para un usuario, se realiza la asignación de permisos solicitados y se le informa al solicitante</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Se solicita la asignación de permisos para un usuario, se realiza la asignación de permisos solicitados y se le informa al solicitante</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1.	Brindar apoyo en la atención de requerimientos técnicos de primer nivel a los usuarios de la Administración Municipal, atendiendo incidentes relacionados con el funcionamiento de equipos de cómputo, impresoras, configuración de software y otros periféricos.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:06:11</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>PLANEACIÓN</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Juan Rodrigo Osorio Urrego  Técnico Operativo</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Se solicita la asignación de permisos para un usuario, se hace la asignación de permisos respectivos y se le informa al solicitante</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Se solicita la asignación de permisos para un usuario, se hace la asignación de permisos respectivos y se le informa al solicitante</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>7.	Colaborar en la implementación y seguimiento de medidas básicas de seguridad informática, tales como el monitoreo de alertas básicas, cierre adecuado de sesiones, y cumplimiento de rutinas establecidas para el uso seguro de los recursos tecnológicos.</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-04-13 14:08:03</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>PROTECCION SOCIAL</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Marleny Alzate Ocampo</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Red/Conectividad</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>LLAMADA TELEFONICA</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Se solicita cambio de contraseña para el equipo del solicitante, se hace el cambio y se le informa al solicitante</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Se solicita cambio de contraseña para el equipo del solicitante, se hace el cambio y se le informa al solicitante</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1.	Brindar apoyo en la atención de requerimientos técnicos de primer nivel a los usuarios de la Administración Municipal, atendiendo incidentes relacionados con el funcionamiento de equipos de cómputo, impresoras, configuración de software y otros periféricos.</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:57:18</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>PLANEACIÓN</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Estefania</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Red/Conectividad</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>LLAMADA TELEFONICA</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Se solicita la revision de la conexión del equipo de computo y el telefono que le proporciona la red de internet al equipo no se encontraba funcionando, a traves de una revision del cableado se hace una revision en el RAC y se desurbre que el cable estaba desconectado, se conecta el cable y vuelve a funcionar normalmente el equipo </t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Se solicita la revision de la conexión del equipo de computo y el telefono que le proporciona la red de internet al equipo no se encontraba funcionando, a traves de una revision del cableado se hace una revision en el RAC y se desurbre que el cable estaba desconectado, se conecta el cable y vuelve a funcionar normalmente el equipo </t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>5.	Realizar seguimiento a solicitudes y requerimientos tecnológicos de los usuarios, documentando novedades, avances y necesidades adicionales, y comunicándolas oportunamente a los responsables correspondientes.</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-04-14 11:59:10</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>IMPUESTOS</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Miguel Salazar</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Se solicita la revision y el presente de una cuenta bloqueda de Saimyr, se hace la solicitud a la mesa de ayuda y resulven el caso, se informa y se evidencia con el funcionario afectado el correcto funcionamiento</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Se solicita la revision y el presente de una cuenta bloqueda de Saimyr, se hace la solicitud a la mesa de ayuda y resulven el caso, se informa y se evidencia con el funcionario afectado el correcto funcionamiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>5.	Realizar seguimiento a solicitudes y requerimientos tecnológicos de los usuarios, documentando novedades, avances y necesidades adicionales, y comunicándolas oportunamente a los responsables correspondientes.</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-04-14 12:01:42</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>IMPUESTOS</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Elizabeth Tibaquira</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Configuración</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>E-MAIL</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Se solicita la asignacion de permisos para que el nuevo funcionario pueda apoyar mas en tema de impuestos, se hace la asignacion correspondiente de los permisos y se le informa a la solicitante</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Se solicita la asignacion de permisos para que el nuevo funcionario pueda apoyar mas en tema de impuestos, se hace la asignacion correspondiente de los permisos y se le informa a la solicitante</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>7.	Colaborar en la implementación y seguimiento de medidas básicas de seguridad informática, tales como el monitoreo de alertas básicas, cierre adecuado de sesiones, y cumplimiento de rutinas establecidas para el uso seguro de los recursos tecnológicos.</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:17:52</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>PROTECCION SOCIAL</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>LLAMADA TELEFONICA</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Se solicita cambio de contraseña del correo electronico para pode ingresar a el correo institucional, se hace el cambio de contraseña y se le evidencia al usuario el ingreso normal al correo electronico</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Se solicita cambio de contraseña del correo electronico para pode ingresar a el correo institucional, se hace el cambio de contraseña y se le evidencia al usuario el ingreso normal al correo electronico</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2.	Apoyar en el mantenimiento preventivo básico de equipos tecnológicos, realizando tareas como limpieza, revisión de cables, conectores y periféricos, con el objetivo de mantener en condiciones óptimas los recursos informáticos de la entidad.</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:20:11</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>PLANEACIÓN</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Angelica</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Red/Conectividad</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>LLAMADA TELEFONICA</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Se solicita la revsion de la conectividad a Red de las caprtas compartidas, se hace la revision correspondiente y se le deja una ip fija, evidenciando que vuelven a funcionar normalmente las carpetas</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Se solicita la revsion de la conectividad a Red de las caprtas compartidas, se hace la revision correspondiente y se le deja una ip fija, evidenciando que vuelven a funcionar normalmente las carpetas</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2.	Apoyar en el mantenimiento preventivo básico de equipos tecnológicos, realizando tareas como limpieza, revisión de cables, conectores y periféricos, con el objetivo de mantener en condiciones óptimas los recursos informáticos de la entidad.</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:23:15</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>PLANEACIÓN</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Walter Dario</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Red/Conectividad</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>LLAMADA TELEFONICA</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Se solicita la conexion a las carpetas de red de la administración se le asigna al equipo una ip fija y se le evidencia al funcionario el correcto funcionamiento</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Se solicita la conexion a las carpetas de red de la administración se le asigna al equipo una ip fija y se le evidencia al funcionario el correcto funcionamiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1.	Brindar apoyo en la atención de requerimientos técnicos de primer nivel a los usuarios de la Administración Municipal, atendiendo incidentes relacionados con el funcionamiento de equipos de cómputo, impresoras, configuración de software y otros periféricos.</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:23:53</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>PLANEACIÓN</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Red/Conectividad</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>VERBAL</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Se solicita la conexion a las carpetas de red de la administración se le asigna al equipo una ip fija y se le evidencia al funcionario el correcto funcionamiento</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Se solicita la conexion a las carpetas de red de la administración se le asigna al equipo una ip fija y se le evidencia al funcionario el correcto funcionamiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1.	Brindar apoyo en la atención de requerimientos técnicos de primer nivel a los usuarios de la Administración Municipal, atendiendo incidentes relacionados con el funcionamiento de equipos de cómputo, impresoras, configuración de software y otros periféricos.</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-04-16 08:25:00</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>PLANEACIÓN</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Angelica</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Impresoras</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>VERBAL</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Se solicita la revision de la conexion a la impresora, se hace la revision correspondiente y se le asigna una ip fija, se le evidencia el normal funcionamiento con la impresora y escaner</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Se solicita la revision de la conexion a la impresora, se hace la revision correspondiente y se le asigna una ip fija, se le evidencia el normal funcionamiento con la impresora y escaner</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Alejandro</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1.	Brindar apoyo en la atención de requerimientos técnicos de primer nivel a los usuarios de la Administración Municipal, atendiendo incidentes relacionados con el funcionamiento de equipos de cómputo, impresoras, configuración de software y otros periféricos.</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-04-16 09:07:19</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>PLANEACIÓN</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Angelica</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Impresoras</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>VERBAL</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Se solicita la revsion de la impresora por un atasco de papel, se retira el atasco y se busca el motivo y se descubre que el fusor de la M636 se le despego el actato, se hace el cambio con un fusor de repuesto y se dejaevidenciado el normal funcionamiento</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Se solicita la revsion de la impresora por un atasco de papel, se retira el atasco y se busca el motivo y se descubre que el fusor de la M636 se le despego el actato, se hace el cambio con un fusor de repuesto y se dejaevidenciado el normal funcionamiento</t>
         </is>
       </c>
     </row>
